--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R464dc873dad34d77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7cbf19290afb4b78"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7cbf19290afb4b78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf570ee29eee54df8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf570ee29eee54df8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78f1673d28b54389"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78f1673d28b54389"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R037616bfec3143d5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R037616bfec3143d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra890f542d47c4bf7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra890f542d47c4bf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf67352c01a23477a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf67352c01a23477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab9975e794a141d8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab9975e794a141d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3fb7636efe44fd0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3fb7636efe44fd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R943789b8fa0444b2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R943789b8fa0444b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc45282a2376e4419"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DataValidation_WholeNumber/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc45282a2376e4419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc9c4885d27284238"/>
   </x:sheets>
 </x:workbook>
 </file>
